--- a/artfynd/A 46782-2025 artfynd.xlsx
+++ b/artfynd/A 46782-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128237144</v>
       </c>
       <c r="B2" t="n">
-        <v>91762</v>
+        <v>91763</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 46782-2025 artfynd.xlsx
+++ b/artfynd/A 46782-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128237144</v>
       </c>
       <c r="B2" t="n">
-        <v>91763</v>
+        <v>91790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 46782-2025 artfynd.xlsx
+++ b/artfynd/A 46782-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128237144</v>
       </c>
       <c r="B2" t="n">
-        <v>91790</v>
+        <v>91800</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
